--- a/content/W03/D5/rubrics/C2_W03_D05_gd_scoring_sheet_TRAINER.xlsx
+++ b/content/W03/D5/rubrics/C2_W03_D05_gd_scoring_sheet_TRAINER.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="58">
   <si>
     <t xml:space="preserve">Build 1 GD scoring sheet (TRAINER ONLY)</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Score from the chair's evidence notes (see gd/C2_W03_D05_gd_facilitation_TRAINER.md), which record each learner's contributions with the minute and the move.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mark an empty seat or an absent learner N in the Sat column; the row then reads absent and drops out of the counts.</t>
+    <t xml:space="preserve">Mark an empty seat or an absent learner N in the Sat column; the row then reads absent and drops out of the counts. A Sat cell left empty reads 'type Y or N in Sat', and the Summary's verdict names it until it is filled.</t>
   </si>
   <si>
     <t xml:space="preserve">The Scores sheet holds 35 seats, one per learner: eight groups of four and G9 of three, as Thursday's roster and Saturday's sheets seat the cohort. Relabel the seats if Monday's allocation put the group of three elsewhere.</t>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t xml:space="preserve">Verdict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows whose Sat cell is neither Y nor N</t>
   </si>
   <si>
     <t xml:space="preserve">Group means, for the Programme Head's read; each learner's own total is the grade</t>
@@ -594,7 +597,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -804,7 +807,7 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="1" t="str">
-        <f aca="false">IF(D3="N","absent",IF(COUNT(H3:K3)&lt;4,"incomplete",SUM(H3:K3)))</f>
+        <f aca="false">IF(D3="N","absent",IF(D3&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H3:K3)&lt;4,"incomplete",SUM(H3:K3))))</f>
         <v>incomplete</v>
       </c>
       <c r="M3" s="1" t="str">
@@ -831,7 +834,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="1" t="str">
-        <f aca="false">IF(D4="N","absent",IF(COUNT(H4:K4)&lt;4,"incomplete",SUM(H4:K4)))</f>
+        <f aca="false">IF(D4="N","absent",IF(D4&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H4:K4)&lt;4,"incomplete",SUM(H4:K4))))</f>
         <v>incomplete</v>
       </c>
       <c r="M4" s="1" t="str">
@@ -858,7 +861,7 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="1" t="str">
-        <f aca="false">IF(D5="N","absent",IF(COUNT(H5:K5)&lt;4,"incomplete",SUM(H5:K5)))</f>
+        <f aca="false">IF(D5="N","absent",IF(D5&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H5:K5)&lt;4,"incomplete",SUM(H5:K5))))</f>
         <v>incomplete</v>
       </c>
       <c r="M5" s="1" t="str">
@@ -885,7 +888,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="1" t="str">
-        <f aca="false">IF(D6="N","absent",IF(COUNT(H6:K6)&lt;4,"incomplete",SUM(H6:K6)))</f>
+        <f aca="false">IF(D6="N","absent",IF(D6&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H6:K6)&lt;4,"incomplete",SUM(H6:K6))))</f>
         <v>incomplete</v>
       </c>
       <c r="M6" s="1" t="str">
@@ -912,7 +915,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="1" t="str">
-        <f aca="false">IF(D7="N","absent",IF(COUNT(H7:K7)&lt;4,"incomplete",SUM(H7:K7)))</f>
+        <f aca="false">IF(D7="N","absent",IF(D7&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H7:K7)&lt;4,"incomplete",SUM(H7:K7))))</f>
         <v>incomplete</v>
       </c>
       <c r="M7" s="1" t="str">
@@ -939,7 +942,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="1" t="str">
-        <f aca="false">IF(D8="N","absent",IF(COUNT(H8:K8)&lt;4,"incomplete",SUM(H8:K8)))</f>
+        <f aca="false">IF(D8="N","absent",IF(D8&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H8:K8)&lt;4,"incomplete",SUM(H8:K8))))</f>
         <v>incomplete</v>
       </c>
       <c r="M8" s="1" t="str">
@@ -966,7 +969,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="1" t="str">
-        <f aca="false">IF(D9="N","absent",IF(COUNT(H9:K9)&lt;4,"incomplete",SUM(H9:K9)))</f>
+        <f aca="false">IF(D9="N","absent",IF(D9&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H9:K9)&lt;4,"incomplete",SUM(H9:K9))))</f>
         <v>incomplete</v>
       </c>
       <c r="M9" s="1" t="str">
@@ -993,7 +996,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="1" t="str">
-        <f aca="false">IF(D10="N","absent",IF(COUNT(H10:K10)&lt;4,"incomplete",SUM(H10:K10)))</f>
+        <f aca="false">IF(D10="N","absent",IF(D10&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H10:K10)&lt;4,"incomplete",SUM(H10:K10))))</f>
         <v>incomplete</v>
       </c>
       <c r="M10" s="1" t="str">
@@ -1020,7 +1023,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="1" t="str">
-        <f aca="false">IF(D11="N","absent",IF(COUNT(H11:K11)&lt;4,"incomplete",SUM(H11:K11)))</f>
+        <f aca="false">IF(D11="N","absent",IF(D11&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H11:K11)&lt;4,"incomplete",SUM(H11:K11))))</f>
         <v>incomplete</v>
       </c>
       <c r="M11" s="1" t="str">
@@ -1047,7 +1050,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="1" t="str">
-        <f aca="false">IF(D12="N","absent",IF(COUNT(H12:K12)&lt;4,"incomplete",SUM(H12:K12)))</f>
+        <f aca="false">IF(D12="N","absent",IF(D12&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H12:K12)&lt;4,"incomplete",SUM(H12:K12))))</f>
         <v>incomplete</v>
       </c>
       <c r="M12" s="1" t="str">
@@ -1074,7 +1077,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="1" t="str">
-        <f aca="false">IF(D13="N","absent",IF(COUNT(H13:K13)&lt;4,"incomplete",SUM(H13:K13)))</f>
+        <f aca="false">IF(D13="N","absent",IF(D13&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H13:K13)&lt;4,"incomplete",SUM(H13:K13))))</f>
         <v>incomplete</v>
       </c>
       <c r="M13" s="1" t="str">
@@ -1101,7 +1104,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="1" t="str">
-        <f aca="false">IF(D14="N","absent",IF(COUNT(H14:K14)&lt;4,"incomplete",SUM(H14:K14)))</f>
+        <f aca="false">IF(D14="N","absent",IF(D14&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H14:K14)&lt;4,"incomplete",SUM(H14:K14))))</f>
         <v>incomplete</v>
       </c>
       <c r="M14" s="1" t="str">
@@ -1128,7 +1131,7 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="1" t="str">
-        <f aca="false">IF(D15="N","absent",IF(COUNT(H15:K15)&lt;4,"incomplete",SUM(H15:K15)))</f>
+        <f aca="false">IF(D15="N","absent",IF(D15&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H15:K15)&lt;4,"incomplete",SUM(H15:K15))))</f>
         <v>incomplete</v>
       </c>
       <c r="M15" s="1" t="str">
@@ -1155,7 +1158,7 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="1" t="str">
-        <f aca="false">IF(D16="N","absent",IF(COUNT(H16:K16)&lt;4,"incomplete",SUM(H16:K16)))</f>
+        <f aca="false">IF(D16="N","absent",IF(D16&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H16:K16)&lt;4,"incomplete",SUM(H16:K16))))</f>
         <v>incomplete</v>
       </c>
       <c r="M16" s="1" t="str">
@@ -1182,7 +1185,7 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="1" t="str">
-        <f aca="false">IF(D17="N","absent",IF(COUNT(H17:K17)&lt;4,"incomplete",SUM(H17:K17)))</f>
+        <f aca="false">IF(D17="N","absent",IF(D17&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H17:K17)&lt;4,"incomplete",SUM(H17:K17))))</f>
         <v>incomplete</v>
       </c>
       <c r="M17" s="1" t="str">
@@ -1209,7 +1212,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="1" t="str">
-        <f aca="false">IF(D18="N","absent",IF(COUNT(H18:K18)&lt;4,"incomplete",SUM(H18:K18)))</f>
+        <f aca="false">IF(D18="N","absent",IF(D18&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H18:K18)&lt;4,"incomplete",SUM(H18:K18))))</f>
         <v>incomplete</v>
       </c>
       <c r="M18" s="1" t="str">
@@ -1236,7 +1239,7 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="1" t="str">
-        <f aca="false">IF(D19="N","absent",IF(COUNT(H19:K19)&lt;4,"incomplete",SUM(H19:K19)))</f>
+        <f aca="false">IF(D19="N","absent",IF(D19&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H19:K19)&lt;4,"incomplete",SUM(H19:K19))))</f>
         <v>incomplete</v>
       </c>
       <c r="M19" s="1" t="str">
@@ -1263,7 +1266,7 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="1" t="str">
-        <f aca="false">IF(D20="N","absent",IF(COUNT(H20:K20)&lt;4,"incomplete",SUM(H20:K20)))</f>
+        <f aca="false">IF(D20="N","absent",IF(D20&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H20:K20)&lt;4,"incomplete",SUM(H20:K20))))</f>
         <v>incomplete</v>
       </c>
       <c r="M20" s="1" t="str">
@@ -1290,7 +1293,7 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="1" t="str">
-        <f aca="false">IF(D21="N","absent",IF(COUNT(H21:K21)&lt;4,"incomplete",SUM(H21:K21)))</f>
+        <f aca="false">IF(D21="N","absent",IF(D21&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H21:K21)&lt;4,"incomplete",SUM(H21:K21))))</f>
         <v>incomplete</v>
       </c>
       <c r="M21" s="1" t="str">
@@ -1317,7 +1320,7 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="1" t="str">
-        <f aca="false">IF(D22="N","absent",IF(COUNT(H22:K22)&lt;4,"incomplete",SUM(H22:K22)))</f>
+        <f aca="false">IF(D22="N","absent",IF(D22&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H22:K22)&lt;4,"incomplete",SUM(H22:K22))))</f>
         <v>incomplete</v>
       </c>
       <c r="M22" s="1" t="str">
@@ -1344,7 +1347,7 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="1" t="str">
-        <f aca="false">IF(D23="N","absent",IF(COUNT(H23:K23)&lt;4,"incomplete",SUM(H23:K23)))</f>
+        <f aca="false">IF(D23="N","absent",IF(D23&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H23:K23)&lt;4,"incomplete",SUM(H23:K23))))</f>
         <v>incomplete</v>
       </c>
       <c r="M23" s="1" t="str">
@@ -1371,7 +1374,7 @@
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="1" t="str">
-        <f aca="false">IF(D24="N","absent",IF(COUNT(H24:K24)&lt;4,"incomplete",SUM(H24:K24)))</f>
+        <f aca="false">IF(D24="N","absent",IF(D24&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H24:K24)&lt;4,"incomplete",SUM(H24:K24))))</f>
         <v>incomplete</v>
       </c>
       <c r="M24" s="1" t="str">
@@ -1398,7 +1401,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="1" t="str">
-        <f aca="false">IF(D25="N","absent",IF(COUNT(H25:K25)&lt;4,"incomplete",SUM(H25:K25)))</f>
+        <f aca="false">IF(D25="N","absent",IF(D25&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H25:K25)&lt;4,"incomplete",SUM(H25:K25))))</f>
         <v>incomplete</v>
       </c>
       <c r="M25" s="1" t="str">
@@ -1425,7 +1428,7 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="1" t="str">
-        <f aca="false">IF(D26="N","absent",IF(COUNT(H26:K26)&lt;4,"incomplete",SUM(H26:K26)))</f>
+        <f aca="false">IF(D26="N","absent",IF(D26&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H26:K26)&lt;4,"incomplete",SUM(H26:K26))))</f>
         <v>incomplete</v>
       </c>
       <c r="M26" s="1" t="str">
@@ -1452,7 +1455,7 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="1" t="str">
-        <f aca="false">IF(D27="N","absent",IF(COUNT(H27:K27)&lt;4,"incomplete",SUM(H27:K27)))</f>
+        <f aca="false">IF(D27="N","absent",IF(D27&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H27:K27)&lt;4,"incomplete",SUM(H27:K27))))</f>
         <v>incomplete</v>
       </c>
       <c r="M27" s="1" t="str">
@@ -1479,7 +1482,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="1" t="str">
-        <f aca="false">IF(D28="N","absent",IF(COUNT(H28:K28)&lt;4,"incomplete",SUM(H28:K28)))</f>
+        <f aca="false">IF(D28="N","absent",IF(D28&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H28:K28)&lt;4,"incomplete",SUM(H28:K28))))</f>
         <v>incomplete</v>
       </c>
       <c r="M28" s="1" t="str">
@@ -1506,7 +1509,7 @@
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="1" t="str">
-        <f aca="false">IF(D29="N","absent",IF(COUNT(H29:K29)&lt;4,"incomplete",SUM(H29:K29)))</f>
+        <f aca="false">IF(D29="N","absent",IF(D29&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H29:K29)&lt;4,"incomplete",SUM(H29:K29))))</f>
         <v>incomplete</v>
       </c>
       <c r="M29" s="1" t="str">
@@ -1533,7 +1536,7 @@
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="1" t="str">
-        <f aca="false">IF(D30="N","absent",IF(COUNT(H30:K30)&lt;4,"incomplete",SUM(H30:K30)))</f>
+        <f aca="false">IF(D30="N","absent",IF(D30&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H30:K30)&lt;4,"incomplete",SUM(H30:K30))))</f>
         <v>incomplete</v>
       </c>
       <c r="M30" s="1" t="str">
@@ -1560,7 +1563,7 @@
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="1" t="str">
-        <f aca="false">IF(D31="N","absent",IF(COUNT(H31:K31)&lt;4,"incomplete",SUM(H31:K31)))</f>
+        <f aca="false">IF(D31="N","absent",IF(D31&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H31:K31)&lt;4,"incomplete",SUM(H31:K31))))</f>
         <v>incomplete</v>
       </c>
       <c r="M31" s="1" t="str">
@@ -1587,7 +1590,7 @@
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="1" t="str">
-        <f aca="false">IF(D32="N","absent",IF(COUNT(H32:K32)&lt;4,"incomplete",SUM(H32:K32)))</f>
+        <f aca="false">IF(D32="N","absent",IF(D32&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H32:K32)&lt;4,"incomplete",SUM(H32:K32))))</f>
         <v>incomplete</v>
       </c>
       <c r="M32" s="1" t="str">
@@ -1614,7 +1617,7 @@
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="1" t="str">
-        <f aca="false">IF(D33="N","absent",IF(COUNT(H33:K33)&lt;4,"incomplete",SUM(H33:K33)))</f>
+        <f aca="false">IF(D33="N","absent",IF(D33&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H33:K33)&lt;4,"incomplete",SUM(H33:K33))))</f>
         <v>incomplete</v>
       </c>
       <c r="M33" s="1" t="str">
@@ -1641,7 +1644,7 @@
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="1" t="str">
-        <f aca="false">IF(D34="N","absent",IF(COUNT(H34:K34)&lt;4,"incomplete",SUM(H34:K34)))</f>
+        <f aca="false">IF(D34="N","absent",IF(D34&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H34:K34)&lt;4,"incomplete",SUM(H34:K34))))</f>
         <v>incomplete</v>
       </c>
       <c r="M34" s="1" t="str">
@@ -1668,7 +1671,7 @@
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="1" t="str">
-        <f aca="false">IF(D35="N","absent",IF(COUNT(H35:K35)&lt;4,"incomplete",SUM(H35:K35)))</f>
+        <f aca="false">IF(D35="N","absent",IF(D35&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H35:K35)&lt;4,"incomplete",SUM(H35:K35))))</f>
         <v>incomplete</v>
       </c>
       <c r="M35" s="1" t="str">
@@ -1695,7 +1698,7 @@
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="1" t="str">
-        <f aca="false">IF(D36="N","absent",IF(COUNT(H36:K36)&lt;4,"incomplete",SUM(H36:K36)))</f>
+        <f aca="false">IF(D36="N","absent",IF(D36&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H36:K36)&lt;4,"incomplete",SUM(H36:K36))))</f>
         <v>incomplete</v>
       </c>
       <c r="M36" s="1" t="str">
@@ -1722,7 +1725,7 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="1" t="str">
-        <f aca="false">IF(D37="N","absent",IF(COUNT(H37:K37)&lt;4,"incomplete",SUM(H37:K37)))</f>
+        <f aca="false">IF(D37="N","absent",IF(D37&lt;&gt;"Y","type Y or N in Sat",IF(COUNT(H37:K37)&lt;4,"incomplete",SUM(H37:K37))))</f>
         <v>incomplete</v>
       </c>
       <c r="M37" s="1" t="str">
@@ -1732,7 +1735,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D3:D37" type="list">
+    <dataValidation allowBlank="false" error="Type Y if the learner sat the round, or N." errorStyle="stop" errorTitle="Sat the round" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D3:D37" type="list">
       <formula1>"Y,N"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1787,7 +1790,7 @@
         <v>50</v>
       </c>
       <c r="B4" s="1" t="n">
-        <f aca="false">COUNT(Scores!L3:L37)</f>
+        <f aca="false">COUNTIFS(Scores!D3:D37,"Y",Scores!L3:L37,"&gt;=0")</f>
         <v>0</v>
       </c>
     </row>
@@ -1814,13 +1817,22 @@
         <v>53</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f aca="false">IF(B5&gt;0,B5&amp;" row(s) hold a score outside the rubric",IF(B4=B3,"every learner who sat a round is scored",B3-B4&amp;" learners still to score"))</f>
+        <f aca="false">IF(B5&gt;0,B5&amp;" row(s) hold a score outside the rubric",IF(B8&gt;0,B8&amp;" row(s) need Y or N in the Sat column",IF(B4=B3,"every learner who sat a round is scored",B3-B4&amp;" learners still to score")))</f>
         <v>35 learners still to score</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <f aca="false">ROWS(Scores!D3:D37)-COUNTIF(Scores!D3:D37,"Y")-COUNTIF(Scores!D3:D37,"N")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1828,10 +1840,10 @@
         <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
